--- a/src/StaticSettingsTests/ValueRendererNullDisplayForSpecificEnum.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererNullDisplayForSpecificEnum.Test.verified.xlsx
@@ -109,10 +109,10 @@
   </sheetData>
   <autoFilter ref="A1:C3"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Antique white." sqref="B2:B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Antique white." prompt="Select one of: Antique white." sqref="B2:B3">
       <formula1>"Antique white"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Build your dream." sqref="C2:C3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Build your dream." prompt="Select one of: Build your dream." sqref="C2:C3">
       <formula1>"Build your dream"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/StaticSettingsTests/ValueRendererNullDisplayForSpecificEnum.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererNullDisplayForSpecificEnum.Test.verified.xlsx
@@ -109,10 +109,10 @@
   </sheetData>
   <autoFilter ref="A1:C3"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Antique white." prompt="Select one of: Antique white." sqref="B2:B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Antique white." prompt="Select one of: Antique white" sqref="B2:B3">
       <formula1>"Antique white"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Build your dream." prompt="Select one of: Build your dream." sqref="C2:C3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Build your dream." prompt="Select one of: Build your dream" sqref="C2:C3">
       <formula1>"Build your dream"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/StaticSettingsTests/ValueRendererNullDisplayForSpecificEnum.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererNullDisplayForSpecificEnum.Test.verified.xlsx
@@ -109,10 +109,10 @@
   </sheetData>
   <autoFilter ref="A1:C3"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Antique white." sqref="B2:B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Antique white." prompt="Select one of: Antique white" sqref="B2:B3">
       <formula1>"Antique white"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Build your dream." sqref="C2:C3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Build your dream." prompt="Select one of: Build your dream" sqref="C2:C3">
       <formula1>"Build your dream"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/StaticSettingsTests/ValueRendererNullDisplayForSpecificEnum.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererNullDisplayForSpecificEnum.Test.verified.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Name"/>
     <column index="2" property="Color"/>
